--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R31d7724480754cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R266d2d0c12894ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R59d590bd077b4ea6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R92d3c21574224e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ree3e117b3ff94e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R1dfdee91f3554f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R65737b1e0c9548d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R08e0e9835ed74e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R0716936d81824147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R7d58070c88844753"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -288,7 +288,7 @@
         <x:v>交付物名称</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
-        <x:v>固定路径或命名规则</x:v>
+        <x:v>固定路径/命名规则</x:v>
       </x:c>
       <x:c r="C1" s="8" t="str">
         <x:v>用途</x:v>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R1dfdee91f3554f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R65737b1e0c9548d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R08e0e9835ed74e12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R0716936d81824147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R7d58070c88844753"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R7c1b0e33476443af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rfff26754997f463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9491f6c76c9d448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R97d87b9e1e614ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R01264bb1b08c45fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -411,13 +411,13 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>旧版本退场表</x:v>
+        <x:v>版本切换表</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
         <x:v>output/results/retirement_gate.csv</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>记录离线存储证据的退场判断</x:v>
+        <x:v>记录各集群的版本切换安排</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>按cluster核对</x:v>
@@ -439,13 +439,13 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>证据范围表</x:v>
+        <x:v>材料范围表</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
         <x:v>output/results/evidence_scope.csv</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
-        <x:v>区分离线快照与静态渲染</x:v>
+        <x:v>记录输入材料与Helm清单的用途</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
         <x:v>按source_file核对</x:v>
@@ -473,7 +473,7 @@
         <x:v>output/README.txt</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
-        <x:v>说明候选包用途与结论边界</x:v>
+        <x:v>说明候选包用途与维护窗分工</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>读取正文</x:v>
